--- a/JsonConverter/ExcelFiles/Weapon.xlsx
+++ b/JsonConverter/ExcelFiles/Weapon.xlsx
@@ -21,46 +21,46 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <x:si>
-    <x:t>고유 ID</x:t>
+    <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>마법팔찌</x:t>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_CoffeeCup_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_Braclet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon_Sword_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>퐁당퐁당 왕국에서 제작된 특별한 검이다.</x:t>
   </x:si>
   <x:si>
     <x:t>일순간 잉여가 될 수 있는 마법의 커피. 시공간을 분리시킨다.</x:t>
   </x:si>
   <x:si>
-    <x:t>퐁당퐁당 왕국에서 제작된 특별한 검이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_Braclet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_CoffeeCup_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon_Sword_1</x:t>
+    <x:t>커피</x:t>
   </x:si>
   <x:si>
     <x:t>검</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
+    <x:t>고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>커피</x:t>
+    <x:t>마법팔찌</x:t>
   </x:si>
   <x:si>
     <x:t>마법을 사용할 수 있는 팔찌</x:t>
@@ -189,7 +189,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -198,7 +198,7 @@
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -213,16 +213,16 @@
     <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -840,31 +840,31 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
     </x:row>
     <x:row r="2" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A3" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
@@ -872,10 +872,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D4" s="4"/>
       <x:c r="E4" s="4"/>
@@ -895,7 +895,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
         <x:v>14</x:v>
@@ -915,13 +915,13 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D6" s="4"/>
       <x:c r="E6" s="4"/>
@@ -2161,7 +2161,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>